--- a/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt1_nucleos.xlsx
@@ -727,13 +727,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8C5A181-DEBE-406E-BD25-436BEE5428DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0D562DA-92D9-40EE-8B8B-B7FDF4F497DE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{857E040C-C4EA-4E06-A735-642E31D5492D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{933777FF-1E99-45B0-9D2D-0BE663170259}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C46AB4D-1B34-4025-B7EC-CE91B43B4F70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D168224E-5C25-4FDC-B3F0-093D830D6204}"/>
 </file>